--- a/test_data/robot.xlsx
+++ b/test_data/robot.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>?????????</t>
+          <t>1 正常验证 get_robot_type（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>????????</t>
+          <t>1 正常验证 get_system_version（ID=1）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
